--- a/photographer_forms/027_picture_day_registration_form--photographer_forms.xlsx
+++ b/photographer_forms/027_picture_day_registration_form--photographer_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -811,8 +811,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -840,12 +840,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'phone',_'value':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Phone', 'value': 'phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -857,12 +857,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'email',_'value':_'email',_'hint':_'please_enter_your_email_address'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Email', 'value': 'email', 'hint': 'Please enter your email address'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -874,12 +874,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'mail',_'value':_'mail'}</t>
+          <t>mail</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Mail', 'value': 'mail'}</t>
+          <t>Mail</t>
         </is>
       </c>
     </row>
@@ -891,12 +891,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_11,_'label':_'landscape',_'value':_'landscape'}</t>
+          <t>landscape</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 11, 'label': 'Landscape', 'value': 'landscape'}</t>
+          <t>Landscape</t>
         </is>
       </c>
     </row>
@@ -908,12 +908,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_12,_'label':_'portrait',_'value':_'portrait'}</t>
+          <t>portrait</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 12, 'label': 'Portrait', 'value': 'portrait'}</t>
+          <t>Portrait</t>
         </is>
       </c>
     </row>
@@ -925,12 +925,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_13,_'label':_'both',_'value':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 13, 'label': 'Both', 'value': 'both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -942,12 +942,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_15,_'label':_'small',_'value':_'small'}</t>
+          <t>small</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 15, 'label': 'Small', 'value': 'small'}</t>
+          <t>Small</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_16,_'label':_'medium',_'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 16, 'label': 'Medium', 'value': 'medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -976,12 +976,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_17,_'label':_'large',_'value':_'large'}</t>
+          <t>large</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 17, 'label': 'Large', 'value': 'large'}</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
@@ -993,12 +993,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_19,_'label':_'jpeg',_'value':_'jpeg'}</t>
+          <t>jpeg</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 19, 'label': 'JPEG', 'value': 'jpeg'}</t>
+          <t>JPEG</t>
         </is>
       </c>
     </row>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_20,_'label':_'png',_'value':_'png'}</t>
+          <t>png</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 20, 'label': 'PNG', 'value': 'png'}</t>
+          <t>PNG</t>
         </is>
       </c>
     </row>
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_21,_'label':_'tiff',_'value':_'tiff'}</t>
+          <t>tiff</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 21, 'label': 'TIFF', 'value': 'tiff'}</t>
+          <t>TIFF</t>
         </is>
       </c>
     </row>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_23,_'label':_'low',_'value':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 23, 'label': 'Low', 'value': 'low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_24,_'label':_'medium',_'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 24, 'label': 'Medium', 'value': 'medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_25,_'label':_'high',_'value':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 25, 'label': 'High', 'value': 'high'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
